--- a/5/search/strategy_visualization/bomb_shielding_details.xlsx
+++ b/5/search/strategy_visualization/bomb_shielding_details.xlsx
@@ -544,40 +544,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FY2</t>
+          <t>FY3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>278.2</v>
+        <v>82</v>
       </c>
       <c r="D4" t="n">
-        <v>139.5</v>
+        <v>125.8</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8</v>
+        <v>21.8</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>7.169999999999975</v>
+        <v>26.22</v>
       </c>
       <c r="H4" t="n">
-        <v>11.11999999999989</v>
+        <v>29.29</v>
       </c>
       <c r="I4" t="n">
-        <v>3.949999999999916</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FY4</t>
+          <t>FY2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -586,64 +586,64 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>292</v>
+        <v>292.8</v>
       </c>
       <c r="D5" t="n">
-        <v>122.7</v>
+        <v>127.6</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>19.37999999999971</v>
+        <v>8.55999999999997</v>
       </c>
       <c r="H5" t="n">
-        <v>22.99999999999964</v>
+        <v>12.54999999999989</v>
       </c>
       <c r="I5" t="n">
-        <v>3.619999999999923</v>
+        <v>3.989999999999915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FY5</t>
+          <t>FY4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>116.2</v>
+        <v>295.4</v>
       </c>
       <c r="D6" t="n">
-        <v>138</v>
+        <v>105.8</v>
       </c>
       <c r="E6" t="n">
-        <v>12.2</v>
+        <v>6.8</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>13.76999999999996</v>
+        <v>17.55999999999978</v>
       </c>
       <c r="H6" t="n">
-        <v>17.52999999999988</v>
+        <v>21.2199999999997</v>
       </c>
       <c r="I6" t="n">
-        <v>3.759999999999918</v>
+        <v>3.659999999999922</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FY3</t>
+          <t>FY5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -652,25 +652,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>87.59999999999999</v>
+        <v>118</v>
       </c>
       <c r="D7" t="n">
-        <v>131.3</v>
+        <v>135.4</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>22.00999999999978</v>
+        <v>13.65999999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>24.85999999999973</v>
+        <v>17.4099999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>2.849999999999941</v>
+        <v>3.749999999999922</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/strategy_visualization/bomb_shielding_details.xlsx
+++ b/5/search/strategy_visualization/bomb_shielding_details.xlsx
@@ -544,40 +544,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FY3</t>
+          <t>FY2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>278.2</v>
       </c>
       <c r="D4" t="n">
-        <v>125.8</v>
+        <v>139.4</v>
       </c>
       <c r="E4" t="n">
-        <v>21.8</v>
+        <v>3.8</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>26.22</v>
+        <v>7.039999999999978</v>
       </c>
       <c r="H4" t="n">
-        <v>29.29</v>
+        <v>11.00999999999989</v>
       </c>
       <c r="I4" t="n">
-        <v>3.07</v>
+        <v>3.969999999999915</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FY2</t>
+          <t>FY4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -586,64 +586,64 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>292.8</v>
+        <v>295.4</v>
       </c>
       <c r="D5" t="n">
-        <v>127.6</v>
+        <v>105.8</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8.55999999999997</v>
+        <v>17.55999999999975</v>
       </c>
       <c r="H5" t="n">
-        <v>12.54999999999989</v>
+        <v>21.21999999999968</v>
       </c>
       <c r="I5" t="n">
-        <v>3.989999999999915</v>
+        <v>3.659999999999922</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FY4</t>
+          <t>FY5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>295.4</v>
+        <v>118</v>
       </c>
       <c r="D6" t="n">
-        <v>105.8</v>
+        <v>135.4</v>
       </c>
       <c r="E6" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>17.55999999999978</v>
+        <v>13.65999999999998</v>
       </c>
       <c r="H6" t="n">
-        <v>21.2199999999997</v>
+        <v>17.4099999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>3.659999999999922</v>
+        <v>3.749999999999922</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FY5</t>
+          <t>FY3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -652,25 +652,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>118</v>
+        <v>82.3</v>
       </c>
       <c r="D7" t="n">
         <v>135.4</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>19.6</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>13.65999999999998</v>
+        <v>21.7799999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>17.4099999999999</v>
+        <v>24.82999999999974</v>
       </c>
       <c r="I7" t="n">
-        <v>3.749999999999922</v>
+        <v>3.049999999999933</v>
       </c>
     </row>
   </sheetData>
